--- a/mock/raw/CP04_unlabeled.xlsx
+++ b/mock/raw/CP04_unlabeled.xlsx
@@ -667,7 +667,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>실링</t>
+          <t>사이드 실링</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
